--- a/src/data/COREP_files/G_EU_C_C0801.xlsx
+++ b/src/data/COREP_files/G_EU_C_C0801.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ33"/>
+  <dimension ref="A1:AH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -789,10 +789,85 @@
           <t>TOTAL EXPOSURES</t>
         </is>
       </c>
+      <c r="D13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E13" t="n">
+        <v>61</v>
+      </c>
+      <c r="F13" t="n">
+        <v>62</v>
+      </c>
+      <c r="G13" t="n">
+        <v>63</v>
+      </c>
+      <c r="H13" t="n">
+        <v>64</v>
+      </c>
+      <c r="I13" t="n">
+        <v>65</v>
+      </c>
+      <c r="J13" t="n">
+        <v>66</v>
+      </c>
+      <c r="K13" t="n">
+        <v>67</v>
+      </c>
+      <c r="L13" t="n">
+        <v>68</v>
+      </c>
+      <c r="N13" t="n">
+        <v>61</v>
+      </c>
+      <c r="P13" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>64</v>
+      </c>
+      <c r="R13" t="n">
+        <v>65</v>
+      </c>
+      <c r="S13" t="n">
+        <v>66</v>
+      </c>
+      <c r="T13" t="n">
+        <v>67</v>
+      </c>
+      <c r="U13" t="n">
+        <v>68</v>
+      </c>
+      <c r="V13" t="n">
+        <v>69</v>
+      </c>
+      <c r="W13" t="n">
+        <v>61</v>
+      </c>
+      <c r="X13" t="n">
+        <v>62</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>63</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>71</v>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
           <t>Cell linked to CA</t>
         </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>68</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -813,6 +888,84 @@
           <t>On balance sheet items subject to credit risk</t>
         </is>
       </c>
+      <c r="D15" t="n">
+        <v>61</v>
+      </c>
+      <c r="E15" t="n">
+        <v>62</v>
+      </c>
+      <c r="F15" t="n">
+        <v>63</v>
+      </c>
+      <c r="G15" t="n">
+        <v>64</v>
+      </c>
+      <c r="H15" t="n">
+        <v>65</v>
+      </c>
+      <c r="I15" t="n">
+        <v>66</v>
+      </c>
+      <c r="J15" t="n">
+        <v>67</v>
+      </c>
+      <c r="K15" t="n">
+        <v>68</v>
+      </c>
+      <c r="L15" t="n">
+        <v>69</v>
+      </c>
+      <c r="N15" t="n">
+        <v>62</v>
+      </c>
+      <c r="P15" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>65</v>
+      </c>
+      <c r="R15" t="n">
+        <v>66</v>
+      </c>
+      <c r="S15" t="n">
+        <v>67</v>
+      </c>
+      <c r="T15" t="n">
+        <v>68</v>
+      </c>
+      <c r="U15" t="n">
+        <v>69</v>
+      </c>
+      <c r="V15" t="n">
+        <v>70</v>
+      </c>
+      <c r="W15" t="n">
+        <v>62</v>
+      </c>
+      <c r="X15" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>64</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>72</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>68</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>69</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>71</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -825,6 +978,84 @@
           <t>Off balance sheet items subject to credit risk</t>
         </is>
       </c>
+      <c r="D16" t="n">
+        <v>62</v>
+      </c>
+      <c r="E16" t="n">
+        <v>63</v>
+      </c>
+      <c r="F16" t="n">
+        <v>64</v>
+      </c>
+      <c r="G16" t="n">
+        <v>65</v>
+      </c>
+      <c r="H16" t="n">
+        <v>66</v>
+      </c>
+      <c r="I16" t="n">
+        <v>67</v>
+      </c>
+      <c r="J16" t="n">
+        <v>68</v>
+      </c>
+      <c r="K16" t="n">
+        <v>69</v>
+      </c>
+      <c r="L16" t="n">
+        <v>70</v>
+      </c>
+      <c r="N16" t="n">
+        <v>63</v>
+      </c>
+      <c r="P16" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>66</v>
+      </c>
+      <c r="R16" t="n">
+        <v>67</v>
+      </c>
+      <c r="S16" t="n">
+        <v>68</v>
+      </c>
+      <c r="T16" t="n">
+        <v>69</v>
+      </c>
+      <c r="U16" t="n">
+        <v>70</v>
+      </c>
+      <c r="V16" t="n">
+        <v>71</v>
+      </c>
+      <c r="W16" t="n">
+        <v>63</v>
+      </c>
+      <c r="X16" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>69</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>71</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>72</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="17">
       <c r="C17" t="inlineStr">
@@ -844,6 +1075,84 @@
           <t>Securities Financing Transactions</t>
         </is>
       </c>
+      <c r="D18" t="n">
+        <v>63</v>
+      </c>
+      <c r="E18" t="n">
+        <v>64</v>
+      </c>
+      <c r="F18" t="n">
+        <v>65</v>
+      </c>
+      <c r="G18" t="n">
+        <v>66</v>
+      </c>
+      <c r="H18" t="n">
+        <v>67</v>
+      </c>
+      <c r="I18" t="n">
+        <v>68</v>
+      </c>
+      <c r="J18" t="n">
+        <v>69</v>
+      </c>
+      <c r="K18" t="n">
+        <v>70</v>
+      </c>
+      <c r="L18" t="n">
+        <v>71</v>
+      </c>
+      <c r="N18" t="n">
+        <v>64</v>
+      </c>
+      <c r="P18" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>67</v>
+      </c>
+      <c r="R18" t="n">
+        <v>68</v>
+      </c>
+      <c r="S18" t="n">
+        <v>69</v>
+      </c>
+      <c r="T18" t="n">
+        <v>70</v>
+      </c>
+      <c r="U18" t="n">
+        <v>71</v>
+      </c>
+      <c r="V18" t="n">
+        <v>72</v>
+      </c>
+      <c r="W18" t="n">
+        <v>64</v>
+      </c>
+      <c r="X18" t="n">
+        <v>65</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>66</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>74</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>71</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>73</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>65</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -856,6 +1165,84 @@
           <t>Derivatives &amp; Long Settlement Transactions</t>
         </is>
       </c>
+      <c r="D19" t="n">
+        <v>64</v>
+      </c>
+      <c r="E19" t="n">
+        <v>65</v>
+      </c>
+      <c r="F19" t="n">
+        <v>66</v>
+      </c>
+      <c r="G19" t="n">
+        <v>67</v>
+      </c>
+      <c r="H19" t="n">
+        <v>68</v>
+      </c>
+      <c r="I19" t="n">
+        <v>69</v>
+      </c>
+      <c r="J19" t="n">
+        <v>70</v>
+      </c>
+      <c r="K19" t="n">
+        <v>71</v>
+      </c>
+      <c r="L19" t="n">
+        <v>72</v>
+      </c>
+      <c r="N19" t="n">
+        <v>65</v>
+      </c>
+      <c r="P19" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>68</v>
+      </c>
+      <c r="R19" t="n">
+        <v>69</v>
+      </c>
+      <c r="S19" t="n">
+        <v>70</v>
+      </c>
+      <c r="T19" t="n">
+        <v>71</v>
+      </c>
+      <c r="U19" t="n">
+        <v>72</v>
+      </c>
+      <c r="V19" t="n">
+        <v>73</v>
+      </c>
+      <c r="W19" t="n">
+        <v>65</v>
+      </c>
+      <c r="X19" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>67</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>72</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>73</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>74</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -868,6 +1255,84 @@
           <t>From Contractual Cross Product Netting</t>
         </is>
       </c>
+      <c r="D20" t="n">
+        <v>65</v>
+      </c>
+      <c r="E20" t="n">
+        <v>66</v>
+      </c>
+      <c r="F20" t="n">
+        <v>67</v>
+      </c>
+      <c r="G20" t="n">
+        <v>68</v>
+      </c>
+      <c r="H20" t="n">
+        <v>69</v>
+      </c>
+      <c r="I20" t="n">
+        <v>70</v>
+      </c>
+      <c r="J20" t="n">
+        <v>71</v>
+      </c>
+      <c r="K20" t="n">
+        <v>72</v>
+      </c>
+      <c r="L20" t="n">
+        <v>73</v>
+      </c>
+      <c r="N20" t="n">
+        <v>66</v>
+      </c>
+      <c r="P20" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>69</v>
+      </c>
+      <c r="R20" t="n">
+        <v>70</v>
+      </c>
+      <c r="S20" t="n">
+        <v>71</v>
+      </c>
+      <c r="T20" t="n">
+        <v>72</v>
+      </c>
+      <c r="U20" t="n">
+        <v>73</v>
+      </c>
+      <c r="V20" t="n">
+        <v>74</v>
+      </c>
+      <c r="W20" t="n">
+        <v>66</v>
+      </c>
+      <c r="X20" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>68</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>76</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>72</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>74</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -880,6 +1345,84 @@
           <t>EXPOSURES ASSIGNED TO OBLIGOR GRADES OR POOLS: TOTAL</t>
         </is>
       </c>
+      <c r="D21" t="n">
+        <v>66</v>
+      </c>
+      <c r="E21" t="n">
+        <v>67</v>
+      </c>
+      <c r="F21" t="n">
+        <v>68</v>
+      </c>
+      <c r="G21" t="n">
+        <v>69</v>
+      </c>
+      <c r="H21" t="n">
+        <v>70</v>
+      </c>
+      <c r="I21" t="n">
+        <v>71</v>
+      </c>
+      <c r="J21" t="n">
+        <v>72</v>
+      </c>
+      <c r="K21" t="n">
+        <v>73</v>
+      </c>
+      <c r="L21" t="n">
+        <v>74</v>
+      </c>
+      <c r="N21" t="n">
+        <v>67</v>
+      </c>
+      <c r="P21" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>70</v>
+      </c>
+      <c r="R21" t="n">
+        <v>71</v>
+      </c>
+      <c r="S21" t="n">
+        <v>72</v>
+      </c>
+      <c r="T21" t="n">
+        <v>73</v>
+      </c>
+      <c r="U21" t="n">
+        <v>74</v>
+      </c>
+      <c r="V21" t="n">
+        <v>75</v>
+      </c>
+      <c r="W21" t="n">
+        <v>67</v>
+      </c>
+      <c r="X21" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>69</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>77</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>76</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>68</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -931,6 +1474,84 @@
       <c r="C26" t="n">
         <v>0.7</v>
       </c>
+      <c r="D26" t="n">
+        <v>61</v>
+      </c>
+      <c r="E26" t="n">
+        <v>62</v>
+      </c>
+      <c r="F26" t="n">
+        <v>63</v>
+      </c>
+      <c r="G26" t="n">
+        <v>64</v>
+      </c>
+      <c r="H26" t="n">
+        <v>65</v>
+      </c>
+      <c r="I26" t="n">
+        <v>66</v>
+      </c>
+      <c r="J26" t="n">
+        <v>67</v>
+      </c>
+      <c r="K26" t="n">
+        <v>68</v>
+      </c>
+      <c r="L26" t="n">
+        <v>69</v>
+      </c>
+      <c r="N26" t="n">
+        <v>62</v>
+      </c>
+      <c r="P26" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>65</v>
+      </c>
+      <c r="R26" t="n">
+        <v>66</v>
+      </c>
+      <c r="S26" t="n">
+        <v>67</v>
+      </c>
+      <c r="T26" t="n">
+        <v>68</v>
+      </c>
+      <c r="U26" t="n">
+        <v>69</v>
+      </c>
+      <c r="V26" t="n">
+        <v>70</v>
+      </c>
+      <c r="W26" t="n">
+        <v>62</v>
+      </c>
+      <c r="X26" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>64</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>72</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>68</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>69</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>71</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -1008,6 +1629,84 @@
         <is>
           <t>DILUTION RISK: TOTAL PURCHASED RECEIVABLES</t>
         </is>
+      </c>
+      <c r="D33" t="n">
+        <v>68</v>
+      </c>
+      <c r="E33" t="n">
+        <v>69</v>
+      </c>
+      <c r="F33" t="n">
+        <v>70</v>
+      </c>
+      <c r="G33" t="n">
+        <v>71</v>
+      </c>
+      <c r="H33" t="n">
+        <v>72</v>
+      </c>
+      <c r="I33" t="n">
+        <v>73</v>
+      </c>
+      <c r="J33" t="n">
+        <v>74</v>
+      </c>
+      <c r="K33" t="n">
+        <v>75</v>
+      </c>
+      <c r="L33" t="n">
+        <v>76</v>
+      </c>
+      <c r="N33" t="n">
+        <v>69</v>
+      </c>
+      <c r="P33" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>72</v>
+      </c>
+      <c r="R33" t="n">
+        <v>73</v>
+      </c>
+      <c r="S33" t="n">
+        <v>74</v>
+      </c>
+      <c r="T33" t="n">
+        <v>75</v>
+      </c>
+      <c r="U33" t="n">
+        <v>76</v>
+      </c>
+      <c r="V33" t="n">
+        <v>77</v>
+      </c>
+      <c r="W33" t="n">
+        <v>69</v>
+      </c>
+      <c r="X33" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>71</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>79</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>76</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>77</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>78</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
